--- a/Doc/화면분석서/DMF0042_BizPlan_UI분석서_v2.0.xlsx
+++ b/Doc/화면분석서/DMF0042_BizPlan_UI분석서_v2.0.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Projects\NSCM\Doc\화면분석서\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E996AD7E-D4F2-41CA-9872-D405E7AF53A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC160E49-289F-4E31-BBC0-8AA200447914}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="360" windowWidth="25760" windowHeight="15440" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="38280" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="1.개요" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="858" uniqueCount="755">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="827" uniqueCount="724">
   <si>
     <t>1. 개요 — 화면정의 · 개정이력</t>
   </si>
@@ -94,12 +94,6 @@
     <t>EDIT_FLAG 행 계산(행 DEPT_ID=내 팀(PM_TEAM_MAPPING 대표화) OR ADMIN) × Measure∈{Business_Plan,LOC} + editLock R1~R6(활성버킷/금년/40 유효구간/insert 화이트리스트/40 Incoterms·FcstType 빈값 개방). GADM·DM_UI_EDITABLE 미사용(0행) — DMF0021/0082 와 방식 상이.</t>
   </si>
   <si>
-    <t>⭐ 선행 산출물 (짝)</t>
-  </si>
-  <si>
-    <t>DMF0042_BizPlan_주요이벤트_상세분석.md (이벤트 8종 — spdMain_Changed L1863~2786 BP/LOC×M·Q·Y 6분기 분할·합산 엔진 등) + DMF0042_BizPlan_제약매트릭스_상세.md (Division 22곳·잠금 73건·팝업 전수 — 1건 1행 원장). 본 분석서 MATRIX 시트는 이를 승계(hook #105 §1-C 0단계).</t>
-  </si>
-  <si>
     <t>2. 전체흐름 — DM 프로세스 내 위치 · 사용 PKG/SP · 주요 테이블 · Measure 저장대상</t>
   </si>
   <si>
@@ -190,9 +184,6 @@
     <t>사업계획 / I/F</t>
   </si>
   <si>
-    <t>사업계획(Biz Plan)을 등록하고, 손익추정 환율 인터페이스(BPS I/F, 1일 2회)와 SCP 로의 NET DEMAND 생성이 이루어지는 단계입니다.</t>
-  </si>
-  <si>
     <t>★ Biz Plan 등록: DMF0042 (본 화면) · NET DEMAND 생성: PR_SCP_PLN_INTERFACE_PLAN</t>
   </si>
   <si>
@@ -214,9 +205,6 @@
     <t>Weekly Rolling: PR_DM_PLN_MKT_FCST_WEEKLY_ROLLING 계열 · 정리: PR_DM_CUTOFF_DATA_CLEANSING</t>
   </si>
   <si>
-    <t>▶ 본 화면의 위치 — DMF0042 는 ⑤ 사업계획 단계의 중심 화면이며, ④ Cutoff 단계의 BP 버전 확정(Ver.Cutoff/Replace)도 직접 수행합니다. ①의 판가·환율과 ②의 시장예측을 받아 사업계획(Business_Plan)과 단가(LOC)를 입력하면, 저장 SP 가 CAR_QTY(81)·환산 금액을 파생 생성하고, 컷오프 시 계획·환율이 버전 스냅샷(_C)으로 확정되어 손익추정(BPS I/F)으로 이어집니다.</t>
-  </si>
-  <si>
     <t>B. 이 화면이 사용하는 PKG · SP (실사용 전수 — 상세는 시트 9 참조)</t>
   </si>
   <si>
@@ -754,24 +742,6 @@
     <t>버튼 disable + 가드</t>
   </si>
   <si>
-    <t>12</t>
-  </si>
-  <si>
-    <t>⚠ orphan</t>
-  </si>
-  <si>
-    <t>MSG00002 (paste 필수값)</t>
-  </si>
-  <si>
-    <t>ValidationCheck 호출처 0 (KeyUp paste 주석화로 사멸) — 탈락 검증 ①.</t>
-  </si>
-  <si>
-    <t>복원 여부 결정 필요 (정직 표기).</t>
-  </si>
-  <si>
-    <t>미구현 명기</t>
-  </si>
-  <si>
     <t>13</t>
   </si>
   <si>
@@ -895,21 +865,6 @@
     <t>근거</t>
   </si>
   <si>
-    <t>조회 브랜치</t>
-  </si>
-  <si>
-    <t>전용 INSERT 브랜치 — End Customer=PROJECT_CODE / BizType=아이템 예측정보 / Dept=Site-Item 부서</t>
-  </si>
-  <si>
-    <t>ELSE 브랜치 — 원본행 DEPT/END_CUSTOMER/BIZ_TYPE</t>
-  </si>
-  <si>
-    <t>(81 과 동일 ELSE 브랜치)</t>
-  </si>
-  <si>
-    <t>GET L347/L500 (원장 단일 — 테이블 분리 없음)</t>
-  </si>
-  <si>
     <t>저장 키 처리</t>
   </si>
   <si>
@@ -1141,21 +1096,6 @@
     <t>L958~1044</t>
   </si>
   <si>
-    <t>SaveData — LOC 행 키</t>
-  </si>
-  <si>
-    <t>END_CUSTOMER40/SITE40/ITEM40/DEPT40/BIZ40 재매핑(재검증 없음)</t>
-  </si>
-  <si>
-    <t>PROJECT/SITE81/PLANT_SITE 전송</t>
-  </si>
-  <si>
-    <t>PROJECT82/SITE82/BIZ82</t>
-  </si>
-  <si>
-    <t>L1075~1118</t>
-  </si>
-  <si>
     <t>InsertRow — 콤보·잠금</t>
   </si>
   <si>
@@ -1291,30 +1231,6 @@
     <t>L762~775</t>
   </si>
   <si>
-    <t>기준일 p_now = 이번주 월요일</t>
-  </si>
-  <si>
-    <t>시작일이 월요일 이후면 from, 종료일이 월요일 이전이면 to+1, 그 외 이번주 월요일</t>
-  </si>
-  <si>
-    <t>SP 과거 보호 기준(서버측)</t>
-  </si>
-  <si>
-    <t>L777~782, 3086~3105</t>
-  </si>
-  <si>
-    <t>Edit: 버킷 외 컬럼 잠금</t>
-  </si>
-  <si>
-    <t>Monthly→비 M_ / Quarterly→비 Q_ / Yearly→비 Y_ 전부 잠금</t>
-  </si>
-  <si>
-    <t>데이터 컬럼</t>
-  </si>
-  <si>
-    <t>L580~637</t>
-  </si>
-  <si>
     <t>Edit: Q_/Y_ 직접입력 차단</t>
   </si>
   <si>
@@ -1423,18 +1339,6 @@
     <t>L1920~2350(BP) / L2352~2783(copy)</t>
   </si>
   <si>
-    <t>⭐ dead 판정 (정직 표기)</t>
-  </si>
-  <si>
-    <t>Yearly 분배의 sDefaultDay 요일 배분 로직은 sDefaultDay 가 선언 후 재할당 없어 런타임 도달 불가</t>
-  </si>
-  <si>
-    <t>(비활성)</t>
-  </si>
-  <si>
-    <t>L2288~2325, 2720~2757 (선언 L206)</t>
-  </si>
-  <si>
     <t>5. MATRIX — 권한 (EDIT_FLAG 행 계산 방식 — DMF0021/0082 와 상이)</t>
   </si>
   <si>
@@ -2294,6 +2198,10 @@
   </si>
   <si>
     <t>DM (Demand) / Demand &gt; Demand Plan &gt; Business Plan — MNU_M: UPPR=Demand_Plan / MNU_MSG_ID=MNU00014 / SORT_ORD=80. MNU_URL 은 구 dmf0042 임시였으나 2026-07-15 business-plan slug 로 정정 완료(3-SET 정합).</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>사업계획(Biz Plan)을 등록하고, 손익추정 환율 인터페이스(BPS I/F, 1일 2회) 생성이 이루어지는 단계입니다.</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
 </sst>
@@ -2376,7 +2284,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -2399,11 +2307,37 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB0B7C3"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FFB0B7C3"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB0B7C3"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FFB0B7C3"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB0B7C3"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB0B7C3"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -2412,6 +2346,9 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -2427,7 +2364,19 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2732,7 +2681,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B14"/>
+  <dimension ref="A1:B13"/>
   <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="22" customWidth="1"/>
@@ -2740,16 +2689,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A1" s="4" t="s">
+      <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="5"/>
+      <c r="B1" s="6"/>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A3" s="6" t="s">
+      <c r="A3" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="5"/>
+      <c r="B3" s="6"/>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A4" s="1" t="s">
@@ -2771,8 +2720,8 @@
       <c r="A6" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B6" s="9" t="s">
-        <v>754</v>
+      <c r="B6" s="4" t="s">
+        <v>722</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="48" x14ac:dyDescent="0.45">
@@ -2829,14 +2778,6 @@
       </c>
       <c r="B13" s="2" t="s">
         <v>20</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" ht="32" x14ac:dyDescent="0.45">
-      <c r="A14" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>22</v>
       </c>
     </row>
   </sheetData>
@@ -2861,27 +2802,27 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A1" s="4" t="s">
-        <v>739</v>
-      </c>
-      <c r="B1" s="5"/>
-      <c r="C1" s="5"/>
-      <c r="D1" s="5"/>
+      <c r="A1" s="5" t="s">
+        <v>707</v>
+      </c>
+      <c r="B1" s="6"/>
+      <c r="C1" s="6"/>
+      <c r="D1" s="6"/>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A3" s="6" t="s">
-        <v>740</v>
-      </c>
-      <c r="B3" s="5"/>
-      <c r="C3" s="5"/>
-      <c r="D3" s="5"/>
+      <c r="A3" s="7" t="s">
+        <v>708</v>
+      </c>
+      <c r="B3" s="6"/>
+      <c r="C3" s="6"/>
+      <c r="D3" s="6"/>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A4" s="1" t="s">
-        <v>651</v>
+        <v>619</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>741</v>
+        <v>709</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>3</v>
@@ -2890,59 +2831,59 @@
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A5" s="2" t="s">
-        <v>742</v>
+        <v>710</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>743</v>
+        <v>711</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>744</v>
+        <v>712</v>
       </c>
       <c r="D5" s="2"/>
     </row>
     <row r="6" spans="1:4" ht="128" x14ac:dyDescent="0.45">
       <c r="A6" s="2" t="s">
-        <v>745</v>
+        <v>713</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>746</v>
+        <v>714</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>747</v>
+        <v>715</v>
       </c>
       <c r="D6" s="2"/>
     </row>
     <row r="7" spans="1:4" ht="48" x14ac:dyDescent="0.45">
       <c r="A7" s="2" t="s">
-        <v>748</v>
+        <v>716</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>749</v>
+        <v>717</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>750</v>
+        <v>718</v>
       </c>
       <c r="D7" s="2"/>
     </row>
     <row r="8" spans="1:4" ht="32" x14ac:dyDescent="0.45">
       <c r="A8" s="2" t="s">
-        <v>742</v>
+        <v>710</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>751</v>
+        <v>719</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>752</v>
+        <v>720</v>
       </c>
       <c r="D8" s="2"/>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A10" s="7" t="s">
-        <v>753</v>
-      </c>
-      <c r="B10" s="5"/>
-      <c r="C10" s="5"/>
-      <c r="D10" s="5"/>
+      <c r="A10" s="8" t="s">
+        <v>721</v>
+      </c>
+      <c r="B10" s="6"/>
+      <c r="C10" s="6"/>
+      <c r="D10" s="6"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -2957,7 +2898,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:F48"/>
+  <dimension ref="A1:F46"/>
   <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="11" customWidth="1"/>
@@ -2969,396 +2910,418 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A1" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="B1" s="5"/>
-      <c r="C1" s="5"/>
-      <c r="D1" s="5"/>
-      <c r="E1" s="5"/>
-      <c r="F1" s="5"/>
+      <c r="A1" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="B1" s="6"/>
+      <c r="C1" s="6"/>
+      <c r="D1" s="6"/>
+      <c r="E1" s="6"/>
+      <c r="F1" s="6"/>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A3" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="B3" s="5"/>
-      <c r="C3" s="5"/>
-      <c r="D3" s="5"/>
-      <c r="E3" s="5"/>
-      <c r="F3" s="5"/>
+      <c r="A3" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="B3" s="6"/>
+      <c r="C3" s="6"/>
+      <c r="D3" s="6"/>
+      <c r="E3" s="6"/>
+      <c r="F3" s="6"/>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A4" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C4" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="D4" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="E4" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D4" s="1" t="s">
+      <c r="F4" s="1" t="s">
         <v>28</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>30</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="48" x14ac:dyDescent="0.45">
       <c r="A5" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="C5" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="D5" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="E5" s="2" t="s">
         <v>33</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>35</v>
       </c>
       <c r="F5" s="2"/>
     </row>
     <row r="6" spans="1:6" ht="48" x14ac:dyDescent="0.45">
       <c r="A6" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="C6" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="D6" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="E6" s="2" t="s">
         <v>38</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>40</v>
       </c>
       <c r="F6" s="2"/>
     </row>
     <row r="7" spans="1:6" ht="32" x14ac:dyDescent="0.45">
       <c r="A7" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="C7" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="D7" s="2" t="s">
         <v>42</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>44</v>
       </c>
       <c r="E7" s="2"/>
       <c r="F7" s="2"/>
     </row>
     <row r="8" spans="1:6" ht="64" x14ac:dyDescent="0.45">
       <c r="A8" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="C8" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="D8" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="C8" s="3" t="s">
+      <c r="E8" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="D8" s="3" t="s">
+      <c r="F8" s="3" t="s">
         <v>48</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="F8" s="3" t="s">
-        <v>50</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="80" x14ac:dyDescent="0.45">
       <c r="A9" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="C9" s="14" t="s">
+        <v>723</v>
+      </c>
+      <c r="D9" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="E9" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="C9" s="3" t="s">
+      <c r="F9" s="3" t="s">
         <v>53</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="F9" s="3" t="s">
-        <v>56</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="48" x14ac:dyDescent="0.45">
       <c r="A10" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="D10" s="2" t="s">
         <v>57</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>60</v>
       </c>
       <c r="E10" s="2"/>
       <c r="F10" s="2"/>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A12" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="B12" s="6"/>
+      <c r="C12" s="6"/>
+      <c r="D12" s="6"/>
+      <c r="E12" s="6"/>
+      <c r="F12" s="6"/>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A13" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="C13" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="B12" s="5"/>
-      <c r="C12" s="5"/>
-      <c r="D12" s="5"/>
-      <c r="E12" s="5"/>
-      <c r="F12" s="5"/>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A14" s="6" t="s">
+      <c r="D13" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="B14" s="5"/>
-      <c r="C14" s="5"/>
-      <c r="D14" s="5"/>
-      <c r="E14" s="5"/>
-      <c r="F14" s="5"/>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A15" s="1" t="s">
+      <c r="E13" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="B15" s="1" t="s">
+      <c r="F13" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" ht="64" x14ac:dyDescent="0.45">
+      <c r="A14" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="C15" s="1" t="s">
+      <c r="B14" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="D15" s="1" t="s">
+      <c r="C14" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="E15" s="1" t="s">
+      <c r="D14" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="F15" s="1" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" ht="64" x14ac:dyDescent="0.45">
+      <c r="E14" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" ht="48" x14ac:dyDescent="0.45">
+      <c r="A15" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" ht="48" x14ac:dyDescent="0.45">
       <c r="A16" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" ht="80" x14ac:dyDescent="0.45">
+      <c r="A17" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="F17" s="2" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" ht="80" x14ac:dyDescent="0.45">
+      <c r="A18" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="E18" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="B16" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="E16" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="F16" s="2" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" ht="48" x14ac:dyDescent="0.45">
-      <c r="A17" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="D17" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="E17" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="F17" s="2" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" ht="48" x14ac:dyDescent="0.45">
-      <c r="A18" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="D18" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="E18" s="2" t="s">
-        <v>84</v>
-      </c>
       <c r="F18" s="2" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" ht="80" x14ac:dyDescent="0.45">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" ht="64" x14ac:dyDescent="0.45">
       <c r="A19" s="2" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="F19" s="2" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" ht="80" x14ac:dyDescent="0.45">
+        <v>92</v>
+      </c>
+      <c r="F19" s="2"/>
+    </row>
+    <row r="20" spans="1:6" ht="32" x14ac:dyDescent="0.45">
       <c r="A20" s="2" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>83</v>
+        <v>99</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="F20" s="2" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" ht="64" x14ac:dyDescent="0.45">
-      <c r="A21" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="B21" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="D21" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="E21" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="F21" s="2"/>
-    </row>
-    <row r="22" spans="1:6" ht="32" x14ac:dyDescent="0.45">
-      <c r="A22" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="B22" s="2" t="s">
+      <c r="F20" s="2"/>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A22" s="7" t="s">
         <v>101</v>
       </c>
-      <c r="C22" s="2" t="s">
+      <c r="B22" s="6"/>
+      <c r="C22" s="6"/>
+      <c r="D22" s="6"/>
+      <c r="E22" s="6"/>
+      <c r="F22" s="6"/>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A23" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B23" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="D22" s="2" t="s">
+      <c r="C23" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="E22" s="2" t="s">
+      <c r="D23" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="F22" s="2"/>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A24" s="6" t="s">
+      <c r="E23" s="1"/>
+      <c r="F23" s="1"/>
+    </row>
+    <row r="24" spans="1:6" ht="64" x14ac:dyDescent="0.45">
+      <c r="A24" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="B24" s="5"/>
-      <c r="C24" s="5"/>
-      <c r="D24" s="5"/>
-      <c r="E24" s="5"/>
-      <c r="F24" s="5"/>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A25" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="B25" s="1" t="s">
+      <c r="B24" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="C25" s="1" t="s">
+      <c r="C24" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="D25" s="1" t="s">
+      <c r="D24" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="E25" s="1"/>
-      <c r="F25" s="1"/>
-    </row>
-    <row r="26" spans="1:6" ht="64" x14ac:dyDescent="0.45">
+      <c r="E24" s="2"/>
+      <c r="F24" s="2"/>
+    </row>
+    <row r="25" spans="1:6" ht="32" x14ac:dyDescent="0.45">
+      <c r="A25" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="E25" s="2"/>
+      <c r="F25" s="2"/>
+    </row>
+    <row r="26" spans="1:6" ht="32" x14ac:dyDescent="0.45">
       <c r="A26" s="2" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="E26" s="2"/>
       <c r="F26" s="2"/>
     </row>
-    <row r="27" spans="1:6" ht="32" x14ac:dyDescent="0.45">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A27" s="2" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="E27" s="2"/>
       <c r="F27" s="2"/>
     </row>
-    <row r="28" spans="1:6" ht="32" x14ac:dyDescent="0.45">
+    <row r="28" spans="1:6" ht="80" x14ac:dyDescent="0.45">
       <c r="A28" s="2" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="D28" s="2" t="s">
         <v>120</v>
@@ -3366,295 +3329,262 @@
       <c r="E28" s="2"/>
       <c r="F28" s="2"/>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="29" spans="1:6" ht="32" x14ac:dyDescent="0.45">
       <c r="A29" s="2" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" s="2"/>
     </row>
     <row r="30" spans="1:6" ht="80" x14ac:dyDescent="0.45">
       <c r="A30" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="E30" s="2"/>
       <c r="F30" s="2"/>
     </row>
-    <row r="31" spans="1:6" ht="32" x14ac:dyDescent="0.45">
+    <row r="31" spans="1:6" ht="64" x14ac:dyDescent="0.45">
       <c r="A31" s="2" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>124</v>
+        <v>133</v>
       </c>
       <c r="E31" s="2"/>
       <c r="F31" s="2"/>
     </row>
-    <row r="32" spans="1:6" ht="80" x14ac:dyDescent="0.45">
+    <row r="32" spans="1:6" ht="48" x14ac:dyDescent="0.45">
       <c r="A32" s="2" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" s="2"/>
     </row>
     <row r="33" spans="1:6" ht="64" x14ac:dyDescent="0.45">
       <c r="A33" s="2" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" s="2"/>
     </row>
-    <row r="34" spans="1:6" ht="48" x14ac:dyDescent="0.45">
+    <row r="34" spans="1:6" ht="64" x14ac:dyDescent="0.45">
       <c r="A34" s="2" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>124</v>
+        <v>143</v>
       </c>
       <c r="E34" s="2"/>
       <c r="F34" s="2"/>
     </row>
-    <row r="35" spans="1:6" ht="64" x14ac:dyDescent="0.45">
+    <row r="35" spans="1:6" ht="160" x14ac:dyDescent="0.45">
       <c r="A35" s="2" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" s="2"/>
     </row>
-    <row r="36" spans="1:6" ht="64" x14ac:dyDescent="0.45">
+    <row r="36" spans="1:6" ht="32" x14ac:dyDescent="0.45">
       <c r="A36" s="2" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>147</v>
+        <v>120</v>
       </c>
       <c r="E36" s="2"/>
       <c r="F36" s="2"/>
     </row>
-    <row r="37" spans="1:6" ht="160" x14ac:dyDescent="0.45">
+    <row r="37" spans="1:6" ht="128" x14ac:dyDescent="0.45">
       <c r="A37" s="2" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>137</v>
+        <v>153</v>
       </c>
       <c r="E37" s="2"/>
       <c r="F37" s="2"/>
     </row>
-    <row r="38" spans="1:6" ht="32" x14ac:dyDescent="0.45">
-      <c r="A38" s="2" t="s">
-        <v>151</v>
-      </c>
-      <c r="B38" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="C38" s="2" t="s">
-        <v>153</v>
-      </c>
-      <c r="D38" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="E38" s="2"/>
-      <c r="F38" s="2"/>
-    </row>
-    <row r="39" spans="1:6" ht="128" x14ac:dyDescent="0.45">
-      <c r="A39" s="2" t="s">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A39" s="7" t="s">
         <v>154</v>
       </c>
-      <c r="B39" s="2" t="s">
+      <c r="B39" s="6"/>
+      <c r="C39" s="6"/>
+      <c r="D39" s="6"/>
+      <c r="E39" s="6"/>
+      <c r="F39" s="6"/>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A40" s="9" t="s">
         <v>155</v>
       </c>
-      <c r="C39" s="2" t="s">
+      <c r="B40" s="6"/>
+      <c r="C40" s="6"/>
+      <c r="D40" s="6"/>
+      <c r="E40" s="6"/>
+      <c r="F40" s="6"/>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A41" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="D39" s="2" t="s">
+      <c r="B41" s="1" t="s">
         <v>157</v>
       </c>
-      <c r="E39" s="2"/>
-      <c r="F39" s="2"/>
-    </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A41" s="6" t="s">
+      <c r="C41" s="1" t="s">
         <v>158</v>
       </c>
-      <c r="B41" s="5"/>
-      <c r="C41" s="5"/>
-      <c r="D41" s="5"/>
-      <c r="E41" s="5"/>
-      <c r="F41" s="5"/>
-    </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A42" s="8" t="s">
+      <c r="D41" s="1"/>
+      <c r="E41" s="1"/>
+      <c r="F41" s="1"/>
+    </row>
+    <row r="42" spans="1:6" ht="80" x14ac:dyDescent="0.45">
+      <c r="A42" s="3" t="s">
         <v>159</v>
       </c>
-      <c r="B42" s="5"/>
-      <c r="C42" s="5"/>
-      <c r="D42" s="5"/>
-      <c r="E42" s="5"/>
-      <c r="F42" s="5"/>
-    </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A43" s="1" t="s">
+      <c r="B42" s="3" t="s">
         <v>160</v>
       </c>
-      <c r="B43" s="1" t="s">
+      <c r="C42" s="3" t="s">
         <v>161</v>
       </c>
-      <c r="C43" s="1" t="s">
+      <c r="D42" s="3"/>
+      <c r="E42" s="3"/>
+      <c r="F42" s="3"/>
+    </row>
+    <row r="43" spans="1:6" ht="48" x14ac:dyDescent="0.45">
+      <c r="A43" s="3" t="s">
         <v>162</v>
       </c>
-      <c r="D43" s="1"/>
-      <c r="E43" s="1"/>
-      <c r="F43" s="1"/>
+      <c r="B43" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="C43" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="D43" s="3"/>
+      <c r="E43" s="3"/>
+      <c r="F43" s="3"/>
     </row>
     <row r="44" spans="1:6" ht="80" x14ac:dyDescent="0.45">
-      <c r="A44" s="3" t="s">
-        <v>163</v>
-      </c>
-      <c r="B44" s="3" t="s">
-        <v>164</v>
-      </c>
-      <c r="C44" s="3" t="s">
+      <c r="A44" s="2" t="s">
         <v>165</v>
       </c>
-      <c r="D44" s="3"/>
-      <c r="E44" s="3"/>
-      <c r="F44" s="3"/>
-    </row>
-    <row r="45" spans="1:6" ht="48" x14ac:dyDescent="0.45">
-      <c r="A45" s="3" t="s">
+      <c r="B44" s="2" t="s">
         <v>166</v>
       </c>
-      <c r="B45" s="3" t="s">
+      <c r="C44" s="2" t="s">
         <v>167</v>
       </c>
-      <c r="C45" s="3" t="s">
+      <c r="D44" s="2"/>
+      <c r="E44" s="2"/>
+      <c r="F44" s="2"/>
+    </row>
+    <row r="45" spans="1:6" ht="64" x14ac:dyDescent="0.45">
+      <c r="A45" s="2" t="s">
         <v>168</v>
       </c>
-      <c r="D45" s="3"/>
-      <c r="E45" s="3"/>
-      <c r="F45" s="3"/>
-    </row>
-    <row r="46" spans="1:6" ht="80" x14ac:dyDescent="0.45">
+      <c r="B45" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="C45" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="D45" s="2"/>
+      <c r="E45" s="2"/>
+      <c r="F45" s="2"/>
+    </row>
+    <row r="46" spans="1:6" ht="32" x14ac:dyDescent="0.45">
       <c r="A46" s="2" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="D46" s="2"/>
       <c r="E46" s="2"/>
       <c r="F46" s="2"/>
     </row>
-    <row r="47" spans="1:6" ht="64" x14ac:dyDescent="0.45">
-      <c r="A47" s="2" t="s">
-        <v>172</v>
-      </c>
-      <c r="B47" s="2" t="s">
-        <v>173</v>
-      </c>
-      <c r="C47" s="2" t="s">
-        <v>174</v>
-      </c>
-      <c r="D47" s="2"/>
-      <c r="E47" s="2"/>
-      <c r="F47" s="2"/>
-    </row>
-    <row r="48" spans="1:6" ht="32" x14ac:dyDescent="0.45">
-      <c r="A48" s="2" t="s">
-        <v>175</v>
-      </c>
-      <c r="B48" s="2" t="s">
-        <v>176</v>
-      </c>
-      <c r="C48" s="2" t="s">
-        <v>177</v>
-      </c>
-      <c r="D48" s="2"/>
-      <c r="E48" s="2"/>
-      <c r="F48" s="2"/>
-    </row>
   </sheetData>
-  <mergeCells count="7">
-    <mergeCell ref="A14:F14"/>
+  <mergeCells count="6">
     <mergeCell ref="A12:F12"/>
-    <mergeCell ref="A42:F42"/>
+    <mergeCell ref="A40:F40"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A3:F3"/>
-    <mergeCell ref="A24:F24"/>
-    <mergeCell ref="A41:F41"/>
+    <mergeCell ref="A22:F22"/>
+    <mergeCell ref="A39:F39"/>
   </mergeCells>
   <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3663,7 +3593,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:F26"/>
+  <dimension ref="A1:F25"/>
   <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
@@ -3675,363 +3605,363 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A1" s="4" t="s">
-        <v>178</v>
-      </c>
-      <c r="B1" s="5"/>
-      <c r="C1" s="5"/>
-      <c r="D1" s="5"/>
-      <c r="E1" s="5"/>
-      <c r="F1" s="5"/>
+      <c r="A1" s="5" t="s">
+        <v>174</v>
+      </c>
+      <c r="B1" s="6"/>
+      <c r="C1" s="6"/>
+      <c r="D1" s="6"/>
+      <c r="E1" s="6"/>
+      <c r="F1" s="6"/>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A3" s="6" t="s">
-        <v>179</v>
-      </c>
-      <c r="B3" s="5"/>
-      <c r="C3" s="5"/>
-      <c r="D3" s="5"/>
-      <c r="E3" s="5"/>
-      <c r="F3" s="5"/>
+      <c r="A3" s="7" t="s">
+        <v>175</v>
+      </c>
+      <c r="B3" s="6"/>
+      <c r="C3" s="6"/>
+      <c r="D3" s="6"/>
+      <c r="E3" s="6"/>
+      <c r="F3" s="6"/>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A4" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="E4" s="1" t="s">
         <v>180</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="F4" s="1" t="s">
         <v>181</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>182</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>183</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>184</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>185</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="32" x14ac:dyDescent="0.45">
       <c r="A5" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="E5" s="2" t="s">
         <v>186</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="F5" s="2" t="s">
         <v>187</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>188</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>189</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>190</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>191</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A6" s="2" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="B6" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="F6" s="2" t="s">
         <v>187</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>193</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>194</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>195</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>191</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A7" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="F7" s="2" t="s">
         <v>196</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>197</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>198</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>199</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>200</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="80" x14ac:dyDescent="0.45">
       <c r="A8" s="2" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="32" x14ac:dyDescent="0.45">
       <c r="A9" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="F9" s="2" t="s">
         <v>205</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>206</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>207</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>208</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>209</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="32" x14ac:dyDescent="0.45">
       <c r="A10" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="F10" s="2" t="s">
         <v>210</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>211</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>212</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>213</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>214</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="32" x14ac:dyDescent="0.45">
       <c r="A11" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="F11" s="2" t="s">
         <v>215</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>216</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>217</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>218</v>
-      </c>
-      <c r="F11" s="2" t="s">
-        <v>219</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A12" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="E12" s="2" t="s">
         <v>220</v>
       </c>
-      <c r="B12" s="2" t="s">
+      <c r="F12" s="2" t="s">
         <v>221</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>222</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>223</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>224</v>
-      </c>
-      <c r="F12" s="2" t="s">
-        <v>225</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="32" x14ac:dyDescent="0.45">
       <c r="A13" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="E13" s="2" t="s">
         <v>226</v>
       </c>
-      <c r="B13" s="2" t="s">
+      <c r="F13" s="2" t="s">
         <v>227</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>228</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>229</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>230</v>
-      </c>
-      <c r="F13" s="2" t="s">
-        <v>231</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="32" x14ac:dyDescent="0.45">
       <c r="A14" s="2" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="32" x14ac:dyDescent="0.45">
       <c r="A15" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>233</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>234</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="F15" s="2" t="s">
         <v>236</v>
       </c>
-      <c r="B15" s="2" t="s">
-        <v>227</v>
-      </c>
-      <c r="C15" s="2" t="s">
+    </row>
+    <row r="16" spans="1:6" ht="48" x14ac:dyDescent="0.45">
+      <c r="A16" s="2" t="s">
         <v>237</v>
       </c>
-      <c r="D15" s="2" t="s">
+      <c r="B16" s="2" t="s">
         <v>238</v>
       </c>
-      <c r="E15" s="2" t="s">
+      <c r="C16" s="2" t="s">
         <v>239</v>
       </c>
-      <c r="F15" s="2" t="s">
+      <c r="D16" s="2" t="s">
         <v>240</v>
       </c>
-    </row>
-    <row r="16" spans="1:6" ht="32" x14ac:dyDescent="0.45">
-      <c r="A16" s="2" t="s">
+      <c r="E16" s="2" t="s">
         <v>241</v>
       </c>
-      <c r="B16" s="2" t="s">
+      <c r="F16" s="2" t="s">
         <v>242</v>
       </c>
-      <c r="C16" s="2" t="s">
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A17" s="9" t="s">
         <v>243</v>
       </c>
-      <c r="D16" s="2" t="s">
+      <c r="B17" s="6"/>
+      <c r="C17" s="6"/>
+      <c r="D17" s="6"/>
+      <c r="E17" s="6"/>
+      <c r="F17" s="6"/>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A19" s="7" t="s">
         <v>244</v>
       </c>
-      <c r="E16" s="2" t="s">
+      <c r="B19" s="6"/>
+      <c r="C19" s="6"/>
+      <c r="D19" s="6"/>
+      <c r="E19" s="6"/>
+      <c r="F19" s="6"/>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A20" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="B20" s="1" t="s">
         <v>245</v>
       </c>
-      <c r="F16" s="2" t="s">
+      <c r="C20" s="1" t="s">
         <v>246</v>
       </c>
-    </row>
-    <row r="17" spans="1:6" ht="48" x14ac:dyDescent="0.45">
-      <c r="A17" s="2" t="s">
+      <c r="D20" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="E20" s="1" t="s">
         <v>247</v>
       </c>
-      <c r="B17" s="2" t="s">
+      <c r="F20" s="1" t="s">
         <v>248</v>
       </c>
-      <c r="C17" s="2" t="s">
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A21" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="B21" s="2" t="s">
         <v>249</v>
       </c>
-      <c r="D17" s="2" t="s">
+      <c r="C21" s="2" t="s">
         <v>250</v>
       </c>
-      <c r="E17" s="2" t="s">
+      <c r="D21" s="2" t="s">
         <v>251</v>
       </c>
-      <c r="F17" s="2" t="s">
+      <c r="E21" s="2" t="s">
         <v>252</v>
       </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A18" s="8" t="s">
+      <c r="F21" s="2" t="s">
         <v>253</v>
       </c>
-      <c r="B18" s="5"/>
-      <c r="C18" s="5"/>
-      <c r="D18" s="5"/>
-      <c r="E18" s="5"/>
-      <c r="F18" s="5"/>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A20" s="6" t="s">
+    </row>
+    <row r="22" spans="1:6" ht="32" x14ac:dyDescent="0.45">
+      <c r="A22" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>249</v>
+      </c>
+      <c r="C22" s="2" t="s">
         <v>254</v>
       </c>
-      <c r="B20" s="5"/>
-      <c r="C20" s="5"/>
-      <c r="D20" s="5"/>
-      <c r="E20" s="5"/>
-      <c r="F20" s="5"/>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A21" s="1" t="s">
-        <v>180</v>
-      </c>
-      <c r="B21" s="1" t="s">
+      <c r="D22" s="2" t="s">
         <v>255</v>
       </c>
-      <c r="C21" s="1" t="s">
+      <c r="E22" s="2" t="s">
         <v>256</v>
       </c>
-      <c r="D21" s="1" t="s">
-        <v>183</v>
-      </c>
-      <c r="E21" s="1" t="s">
+      <c r="F22" s="2" t="s">
         <v>257</v>
-      </c>
-      <c r="F21" s="1" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A22" s="2" t="s">
-        <v>186</v>
-      </c>
-      <c r="B22" s="2" t="s">
-        <v>259</v>
-      </c>
-      <c r="C22" s="2" t="s">
-        <v>260</v>
-      </c>
-      <c r="D22" s="2" t="s">
-        <v>261</v>
-      </c>
-      <c r="E22" s="2" t="s">
-        <v>262</v>
-      </c>
-      <c r="F22" s="2" t="s">
-        <v>263</v>
       </c>
     </row>
     <row r="23" spans="1:6" ht="32" x14ac:dyDescent="0.45">
@@ -4039,39 +3969,39 @@
         <v>192</v>
       </c>
       <c r="B23" s="2" t="s">
+        <v>249</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="D23" s="2" t="s">
         <v>259</v>
       </c>
-      <c r="C23" s="2" t="s">
+      <c r="E23" s="2" t="s">
+        <v>260</v>
+      </c>
+      <c r="F23" s="2" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" ht="48" x14ac:dyDescent="0.45">
+      <c r="A24" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>261</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>262</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>263</v>
+      </c>
+      <c r="E24" s="2" t="s">
         <v>264</v>
       </c>
-      <c r="D23" s="2" t="s">
+      <c r="F24" s="2" t="s">
         <v>265</v>
-      </c>
-      <c r="E23" s="2" t="s">
-        <v>266</v>
-      </c>
-      <c r="F23" s="2" t="s">
-        <v>267</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6" ht="32" x14ac:dyDescent="0.45">
-      <c r="A24" s="2" t="s">
-        <v>196</v>
-      </c>
-      <c r="B24" s="2" t="s">
-        <v>259</v>
-      </c>
-      <c r="C24" s="2" t="s">
-        <v>268</v>
-      </c>
-      <c r="D24" s="2" t="s">
-        <v>269</v>
-      </c>
-      <c r="E24" s="2" t="s">
-        <v>270</v>
-      </c>
-      <c r="F24" s="2" t="s">
-        <v>110</v>
       </c>
     </row>
     <row r="25" spans="1:6" ht="48" x14ac:dyDescent="0.45">
@@ -4079,45 +4009,25 @@
         <v>201</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>272</v>
+        <v>267</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>273</v>
+        <v>268</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>274</v>
+        <v>269</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>275</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6" ht="48" x14ac:dyDescent="0.45">
-      <c r="A26" s="2" t="s">
-        <v>205</v>
-      </c>
-      <c r="B26" s="2" t="s">
-        <v>276</v>
-      </c>
-      <c r="C26" s="2" t="s">
-        <v>277</v>
-      </c>
-      <c r="D26" s="2" t="s">
-        <v>278</v>
-      </c>
-      <c r="E26" s="2" t="s">
-        <v>279</v>
-      </c>
-      <c r="F26" s="2" t="s">
-        <v>280</v>
+        <v>270</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="4">
-    <mergeCell ref="A18:F18"/>
-    <mergeCell ref="A20:F20"/>
+    <mergeCell ref="A17:F17"/>
+    <mergeCell ref="A19:F19"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A3:F3"/>
   </mergeCells>
@@ -4128,7 +4038,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:F49"/>
+  <dimension ref="A1:F44"/>
   <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="24" customWidth="1"/>
@@ -4138,725 +4048,646 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A1" s="4" t="s">
-        <v>281</v>
-      </c>
-      <c r="B1" s="5"/>
-      <c r="C1" s="5"/>
-      <c r="D1" s="5"/>
-      <c r="E1" s="5"/>
-      <c r="F1" s="5"/>
+      <c r="A1" s="5" t="s">
+        <v>271</v>
+      </c>
+      <c r="B1" s="6"/>
+      <c r="C1" s="6"/>
+      <c r="D1" s="6"/>
+      <c r="E1" s="6"/>
+      <c r="F1" s="6"/>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A3" s="6" t="s">
-        <v>282</v>
-      </c>
-      <c r="B3" s="5"/>
-      <c r="C3" s="5"/>
-      <c r="D3" s="5"/>
-      <c r="E3" s="5"/>
+      <c r="A3" s="7" t="s">
+        <v>272</v>
+      </c>
+      <c r="B3" s="6"/>
+      <c r="C3" s="6"/>
+      <c r="D3" s="6"/>
+      <c r="E3" s="6"/>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A4" s="1" t="s">
-        <v>283</v>
+        <v>273</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>284</v>
+        <v>274</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>285</v>
+        <v>275</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>286</v>
+        <v>276</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>287</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" ht="48" x14ac:dyDescent="0.45">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="32" x14ac:dyDescent="0.45">
       <c r="A5" s="2" t="s">
-        <v>288</v>
+        <v>278</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>289</v>
+        <v>279</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>290</v>
+        <v>280</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>291</v>
+        <v>280</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>292</v>
+        <v>281</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="32" x14ac:dyDescent="0.45">
       <c r="A6" s="2" t="s">
-        <v>293</v>
+        <v>282</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>294</v>
+        <v>283</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>295</v>
+        <v>284</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>295</v>
+        <v>285</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>296</v>
+        <v>286</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="32" x14ac:dyDescent="0.45">
       <c r="A7" s="2" t="s">
-        <v>297</v>
+        <v>287</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>298</v>
+        <v>288</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>299</v>
+        <v>289</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>300</v>
+        <v>290</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>301</v>
+        <v>291</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="32" x14ac:dyDescent="0.45">
       <c r="A8" s="2" t="s">
-        <v>302</v>
+        <v>292</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>303</v>
+        <v>293</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>304</v>
+        <v>294</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>305</v>
+        <v>295</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>306</v>
+        <v>296</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="32" x14ac:dyDescent="0.45">
       <c r="A9" s="2" t="s">
-        <v>307</v>
+        <v>297</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>308</v>
+        <v>298</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>309</v>
+        <v>299</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>310</v>
+        <v>300</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>311</v>
+        <v>301</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="32" x14ac:dyDescent="0.45">
       <c r="A10" s="2" t="s">
+        <v>302</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>303</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>304</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>305</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" ht="48" x14ac:dyDescent="0.45">
+      <c r="A11" s="2" t="s">
+        <v>307</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>308</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>309</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>310</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" ht="32" x14ac:dyDescent="0.45">
+      <c r="A12" s="2" t="s">
         <v>312</v>
       </c>
-      <c r="B10" s="2" t="s">
+      <c r="B12" s="2" t="s">
         <v>313</v>
       </c>
-      <c r="C10" s="2" t="s">
+      <c r="C12" s="2" t="s">
         <v>314</v>
       </c>
-      <c r="D10" s="2" t="s">
+      <c r="D12" s="2" t="s">
         <v>315</v>
       </c>
-      <c r="E10" s="2" t="s">
+      <c r="E12" s="2" t="s">
         <v>316</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" ht="32" x14ac:dyDescent="0.45">
-      <c r="A11" s="2" t="s">
-        <v>317</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>318</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>319</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>320</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" ht="48" x14ac:dyDescent="0.45">
-      <c r="A12" s="2" t="s">
-        <v>322</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>323</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>324</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>325</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>326</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="32" x14ac:dyDescent="0.45">
       <c r="A13" s="2" t="s">
+        <v>317</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>318</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>319</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>319</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A15" s="7" t="s">
+        <v>321</v>
+      </c>
+      <c r="B15" s="6"/>
+      <c r="C15" s="6"/>
+      <c r="D15" s="6"/>
+      <c r="E15" s="6"/>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A16" s="1" t="s">
+        <v>322</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>324</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>325</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" ht="48" x14ac:dyDescent="0.45">
+      <c r="A17" s="2" t="s">
         <v>327</v>
       </c>
-      <c r="B13" s="2" t="s">
+      <c r="B17" s="2" t="s">
         <v>328</v>
       </c>
-      <c r="C13" s="2" t="s">
+      <c r="C17" s="2" t="s">
         <v>329</v>
       </c>
-      <c r="D13" s="2" t="s">
+      <c r="D17" s="2" t="s">
         <v>330</v>
       </c>
-      <c r="E13" s="2" t="s">
+      <c r="E17" s="2" t="s">
         <v>331</v>
       </c>
     </row>
-    <row r="14" spans="1:6" ht="32" x14ac:dyDescent="0.45">
-      <c r="A14" s="2" t="s">
+    <row r="18" spans="1:5" ht="32" x14ac:dyDescent="0.45">
+      <c r="A18" s="2" t="s">
         <v>332</v>
       </c>
-      <c r="B14" s="2" t="s">
+      <c r="B18" s="2" t="s">
         <v>333</v>
       </c>
-      <c r="C14" s="2" t="s">
+      <c r="C18" s="2" t="s">
         <v>334</v>
       </c>
-      <c r="D14" s="2" t="s">
-        <v>334</v>
-      </c>
-      <c r="E14" s="2" t="s">
+      <c r="D18" s="2" t="s">
+        <v>319</v>
+      </c>
+      <c r="E18" s="2" t="s">
         <v>335</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A16" s="6" t="s">
-        <v>336</v>
-      </c>
-      <c r="B16" s="5"/>
-      <c r="C16" s="5"/>
-      <c r="D16" s="5"/>
-      <c r="E16" s="5"/>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A17" s="1" t="s">
-        <v>337</v>
-      </c>
-      <c r="B17" s="1" t="s">
-        <v>338</v>
-      </c>
-      <c r="C17" s="1" t="s">
-        <v>339</v>
-      </c>
-      <c r="D17" s="1" t="s">
-        <v>340</v>
-      </c>
-      <c r="E17" s="1" t="s">
-        <v>341</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" ht="48" x14ac:dyDescent="0.45">
-      <c r="A18" s="2" t="s">
-        <v>342</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>343</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>344</v>
-      </c>
-      <c r="D18" s="2" t="s">
-        <v>345</v>
-      </c>
-      <c r="E18" s="2" t="s">
-        <v>346</v>
       </c>
     </row>
     <row r="19" spans="1:5" ht="32" x14ac:dyDescent="0.45">
       <c r="A19" s="2" t="s">
-        <v>347</v>
+        <v>336</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>348</v>
+        <v>337</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>349</v>
+        <v>338</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>334</v>
+        <v>319</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" ht="32" x14ac:dyDescent="0.45">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A20" s="2" t="s">
-        <v>351</v>
+        <v>340</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>352</v>
+        <v>341</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>353</v>
+        <v>342</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>334</v>
+        <v>343</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>354</v>
+        <v>344</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A21" s="2" t="s">
+        <v>345</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>346</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>347</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>348</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" ht="64" x14ac:dyDescent="0.45">
+      <c r="A22" s="2" t="s">
+        <v>350</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>351</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>352</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>353</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" ht="32" x14ac:dyDescent="0.45">
+      <c r="A23" s="2" t="s">
         <v>355</v>
       </c>
-      <c r="B21" s="2" t="s">
+      <c r="B23" s="2" t="s">
         <v>356</v>
       </c>
-      <c r="C21" s="2" t="s">
+      <c r="C23" s="2" t="s">
         <v>357</v>
       </c>
-      <c r="D21" s="2" t="s">
+      <c r="D23" s="2" t="s">
         <v>358</v>
       </c>
-      <c r="E21" s="2" t="s">
+      <c r="E23" s="2" t="s">
         <v>359</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A22" s="2" t="s">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A24" s="2" t="s">
         <v>360</v>
       </c>
-      <c r="B22" s="2" t="s">
+      <c r="B24" s="2" t="s">
         <v>361</v>
       </c>
-      <c r="C22" s="2" t="s">
+      <c r="C24" s="2" t="s">
         <v>362</v>
       </c>
-      <c r="D22" s="2" t="s">
+      <c r="D24" s="2" t="s">
+        <v>319</v>
+      </c>
+      <c r="E24" s="2" t="s">
         <v>363</v>
-      </c>
-      <c r="E22" s="2" t="s">
-        <v>364</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" ht="64" x14ac:dyDescent="0.45">
-      <c r="A23" s="2" t="s">
-        <v>365</v>
-      </c>
-      <c r="B23" s="2" t="s">
-        <v>366</v>
-      </c>
-      <c r="C23" s="2" t="s">
-        <v>367</v>
-      </c>
-      <c r="D23" s="2" t="s">
-        <v>368</v>
-      </c>
-      <c r="E23" s="2" t="s">
-        <v>369</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5" ht="32" x14ac:dyDescent="0.45">
-      <c r="A24" s="2" t="s">
-        <v>370</v>
-      </c>
-      <c r="B24" s="2" t="s">
-        <v>371</v>
-      </c>
-      <c r="C24" s="2" t="s">
-        <v>372</v>
-      </c>
-      <c r="D24" s="2" t="s">
-        <v>373</v>
-      </c>
-      <c r="E24" s="2" t="s">
-        <v>374</v>
       </c>
     </row>
     <row r="25" spans="1:5" ht="32" x14ac:dyDescent="0.45">
       <c r="A25" s="2" t="s">
+        <v>364</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>365</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>319</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>319</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" ht="32" x14ac:dyDescent="0.45">
+      <c r="A26" s="2" t="s">
+        <v>367</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>368</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>369</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>370</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" ht="48" x14ac:dyDescent="0.45">
+      <c r="A27" s="2" t="s">
+        <v>372</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>373</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>374</v>
+      </c>
+      <c r="D27" s="2" t="s">
         <v>375</v>
       </c>
-      <c r="B25" s="2" t="s">
+      <c r="E27" s="2" t="s">
         <v>376</v>
-      </c>
-      <c r="C25" s="2" t="s">
-        <v>377</v>
-      </c>
-      <c r="D25" s="2" t="s">
-        <v>378</v>
-      </c>
-      <c r="E25" s="2" t="s">
-        <v>379</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A26" s="2" t="s">
-        <v>380</v>
-      </c>
-      <c r="B26" s="2" t="s">
-        <v>381</v>
-      </c>
-      <c r="C26" s="2" t="s">
-        <v>382</v>
-      </c>
-      <c r="D26" s="2" t="s">
-        <v>334</v>
-      </c>
-      <c r="E26" s="2" t="s">
-        <v>383</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5" ht="32" x14ac:dyDescent="0.45">
-      <c r="A27" s="2" t="s">
-        <v>384</v>
-      </c>
-      <c r="B27" s="2" t="s">
-        <v>385</v>
-      </c>
-      <c r="C27" s="2" t="s">
-        <v>334</v>
-      </c>
-      <c r="D27" s="2" t="s">
-        <v>334</v>
-      </c>
-      <c r="E27" s="2" t="s">
-        <v>386</v>
       </c>
     </row>
     <row r="28" spans="1:5" ht="32" x14ac:dyDescent="0.45">
       <c r="A28" s="2" t="s">
+        <v>377</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>378</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>379</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>380</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A29" s="2" t="s">
+        <v>382</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>383</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>384</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>385</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A30" s="9" t="s">
         <v>387</v>
       </c>
-      <c r="B28" s="2" t="s">
+      <c r="B30" s="6"/>
+      <c r="C30" s="6"/>
+      <c r="D30" s="6"/>
+      <c r="E30" s="6"/>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A32" s="7" t="s">
         <v>388</v>
       </c>
-      <c r="C28" s="2" t="s">
+      <c r="B32" s="6"/>
+      <c r="C32" s="6"/>
+      <c r="D32" s="6"/>
+      <c r="E32" s="6"/>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A33" s="1" t="s">
         <v>389</v>
       </c>
-      <c r="D28" s="2" t="s">
+      <c r="B33" s="1" t="s">
         <v>390</v>
       </c>
-      <c r="E28" s="2" t="s">
+      <c r="C33" s="1" t="s">
         <v>391</v>
       </c>
-    </row>
-    <row r="29" spans="1:5" ht="48" x14ac:dyDescent="0.45">
-      <c r="A29" s="2" t="s">
+      <c r="D33" s="1"/>
+      <c r="E33" s="1" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" ht="64" x14ac:dyDescent="0.45">
+      <c r="A34" s="2" t="s">
         <v>392</v>
       </c>
-      <c r="B29" s="2" t="s">
+      <c r="B34" s="2" t="s">
         <v>393</v>
       </c>
-      <c r="C29" s="2" t="s">
+      <c r="C34" s="2" t="s">
         <v>394</v>
       </c>
-      <c r="D29" s="2" t="s">
+      <c r="D34" s="2"/>
+      <c r="E34" s="2" t="s">
         <v>395</v>
       </c>
-      <c r="E29" s="2" t="s">
+    </row>
+    <row r="35" spans="1:5" ht="32" x14ac:dyDescent="0.45">
+      <c r="A35" s="2" t="s">
         <v>396</v>
       </c>
-    </row>
-    <row r="30" spans="1:5" ht="32" x14ac:dyDescent="0.45">
-      <c r="A30" s="2" t="s">
+      <c r="B35" s="2" t="s">
         <v>397</v>
       </c>
-      <c r="B30" s="2" t="s">
+      <c r="C35" s="2" t="s">
         <v>398</v>
       </c>
-      <c r="C30" s="2" t="s">
+      <c r="D35" s="2"/>
+      <c r="E35" s="2" t="s">
         <v>399</v>
       </c>
-      <c r="D30" s="2" t="s">
+    </row>
+    <row r="36" spans="1:5" ht="32" x14ac:dyDescent="0.45">
+      <c r="A36" s="2" t="s">
         <v>400</v>
       </c>
-      <c r="E30" s="2" t="s">
+      <c r="B36" s="2" t="s">
         <v>401</v>
       </c>
-    </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A31" s="2" t="s">
+      <c r="C36" s="2" t="s">
         <v>402</v>
-      </c>
-      <c r="B31" s="2" t="s">
-        <v>403</v>
-      </c>
-      <c r="C31" s="2" t="s">
-        <v>404</v>
-      </c>
-      <c r="D31" s="2" t="s">
-        <v>405</v>
-      </c>
-      <c r="E31" s="2" t="s">
-        <v>406</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A32" s="8" t="s">
-        <v>407</v>
-      </c>
-      <c r="B32" s="5"/>
-      <c r="C32" s="5"/>
-      <c r="D32" s="5"/>
-      <c r="E32" s="5"/>
-    </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A34" s="6" t="s">
-        <v>408</v>
-      </c>
-      <c r="B34" s="5"/>
-      <c r="C34" s="5"/>
-      <c r="D34" s="5"/>
-      <c r="E34" s="5"/>
-    </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A35" s="1" t="s">
-        <v>409</v>
-      </c>
-      <c r="B35" s="1" t="s">
-        <v>410</v>
-      </c>
-      <c r="C35" s="1" t="s">
-        <v>411</v>
-      </c>
-      <c r="D35" s="1"/>
-      <c r="E35" s="1" t="s">
-        <v>341</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5" ht="64" x14ac:dyDescent="0.45">
-      <c r="A36" s="2" t="s">
-        <v>412</v>
-      </c>
-      <c r="B36" s="2" t="s">
-        <v>413</v>
-      </c>
-      <c r="C36" s="2" t="s">
-        <v>414</v>
       </c>
       <c r="D36" s="2"/>
       <c r="E36" s="2" t="s">
-        <v>415</v>
+        <v>403</v>
       </c>
     </row>
     <row r="37" spans="1:5" ht="32" x14ac:dyDescent="0.45">
       <c r="A37" s="2" t="s">
-        <v>416</v>
+        <v>404</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>417</v>
+        <v>405</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>418</v>
+        <v>406</v>
       </c>
       <c r="D37" s="2"/>
       <c r="E37" s="2" t="s">
-        <v>419</v>
+        <v>407</v>
       </c>
     </row>
     <row r="38" spans="1:5" ht="32" x14ac:dyDescent="0.45">
       <c r="A38" s="2" t="s">
-        <v>420</v>
+        <v>408</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>421</v>
+        <v>409</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>422</v>
+        <v>410</v>
       </c>
       <c r="D38" s="2"/>
       <c r="E38" s="2" t="s">
-        <v>423</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5" ht="32" x14ac:dyDescent="0.45">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" ht="48" x14ac:dyDescent="0.45">
       <c r="A39" s="2" t="s">
-        <v>424</v>
+        <v>412</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>425</v>
+        <v>413</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>426</v>
+        <v>414</v>
       </c>
       <c r="D39" s="2"/>
       <c r="E39" s="2" t="s">
-        <v>427</v>
+        <v>415</v>
       </c>
     </row>
     <row r="40" spans="1:5" ht="32" x14ac:dyDescent="0.45">
       <c r="A40" s="2" t="s">
-        <v>428</v>
+        <v>416</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>429</v>
+        <v>417</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>430</v>
+        <v>418</v>
       </c>
       <c r="D40" s="2"/>
       <c r="E40" s="2" t="s">
-        <v>431</v>
+        <v>419</v>
       </c>
     </row>
     <row r="41" spans="1:5" ht="32" x14ac:dyDescent="0.45">
       <c r="A41" s="2" t="s">
-        <v>432</v>
+        <v>420</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>433</v>
+        <v>421</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>434</v>
+        <v>422</v>
       </c>
       <c r="D41" s="2"/>
       <c r="E41" s="2" t="s">
-        <v>435</v>
+        <v>423</v>
       </c>
     </row>
     <row r="42" spans="1:5" ht="32" x14ac:dyDescent="0.45">
       <c r="A42" s="2" t="s">
-        <v>436</v>
+        <v>424</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>437</v>
+        <v>425</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>438</v>
+        <v>426</v>
       </c>
       <c r="D42" s="2"/>
       <c r="E42" s="2" t="s">
-        <v>439</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5" ht="48" x14ac:dyDescent="0.45">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" ht="32" x14ac:dyDescent="0.45">
       <c r="A43" s="2" t="s">
-        <v>440</v>
+        <v>428</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>441</v>
+        <v>429</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>442</v>
+        <v>430</v>
       </c>
       <c r="D43" s="2"/>
       <c r="E43" s="2" t="s">
-        <v>443</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5" ht="32" x14ac:dyDescent="0.45">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" ht="80" x14ac:dyDescent="0.45">
       <c r="A44" s="2" t="s">
-        <v>444</v>
+        <v>432</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>445</v>
+        <v>433</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>446</v>
+        <v>434</v>
       </c>
       <c r="D44" s="2"/>
       <c r="E44" s="2" t="s">
-        <v>447</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5" ht="32" x14ac:dyDescent="0.45">
-      <c r="A45" s="2" t="s">
-        <v>448</v>
-      </c>
-      <c r="B45" s="2" t="s">
-        <v>449</v>
-      </c>
-      <c r="C45" s="2" t="s">
-        <v>450</v>
-      </c>
-      <c r="D45" s="2"/>
-      <c r="E45" s="2" t="s">
-        <v>451</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5" ht="32" x14ac:dyDescent="0.45">
-      <c r="A46" s="2" t="s">
-        <v>452</v>
-      </c>
-      <c r="B46" s="2" t="s">
-        <v>453</v>
-      </c>
-      <c r="C46" s="2" t="s">
-        <v>454</v>
-      </c>
-      <c r="D46" s="2"/>
-      <c r="E46" s="2" t="s">
-        <v>455</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5" ht="32" x14ac:dyDescent="0.45">
-      <c r="A47" s="2" t="s">
-        <v>456</v>
-      </c>
-      <c r="B47" s="2" t="s">
-        <v>457</v>
-      </c>
-      <c r="C47" s="2" t="s">
-        <v>458</v>
-      </c>
-      <c r="D47" s="2"/>
-      <c r="E47" s="2" t="s">
-        <v>459</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5" ht="80" x14ac:dyDescent="0.45">
-      <c r="A48" s="2" t="s">
-        <v>460</v>
-      </c>
-      <c r="B48" s="2" t="s">
-        <v>461</v>
-      </c>
-      <c r="C48" s="2" t="s">
-        <v>462</v>
-      </c>
-      <c r="D48" s="2"/>
-      <c r="E48" s="2" t="s">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5" ht="48" x14ac:dyDescent="0.45">
-      <c r="A49" s="2" t="s">
-        <v>464</v>
-      </c>
-      <c r="B49" s="2" t="s">
-        <v>465</v>
-      </c>
-      <c r="C49" s="2" t="s">
-        <v>466</v>
-      </c>
-      <c r="D49" s="2"/>
-      <c r="E49" s="2" t="s">
-        <v>467</v>
+        <v>435</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="5">
-    <mergeCell ref="A32:E32"/>
+    <mergeCell ref="A30:E30"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A3:E3"/>
-    <mergeCell ref="A34:E34"/>
-    <mergeCell ref="A16:E16"/>
+    <mergeCell ref="A32:E32"/>
+    <mergeCell ref="A15:E15"/>
   </mergeCells>
   <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4876,441 +4707,441 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A1" s="4" t="s">
-        <v>468</v>
-      </c>
-      <c r="B1" s="5"/>
-      <c r="C1" s="5"/>
-      <c r="D1" s="5"/>
-      <c r="E1" s="5"/>
-      <c r="F1" s="5"/>
+      <c r="A1" s="5" t="s">
+        <v>436</v>
+      </c>
+      <c r="B1" s="6"/>
+      <c r="C1" s="6"/>
+      <c r="D1" s="6"/>
+      <c r="E1" s="6"/>
+      <c r="F1" s="6"/>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A3" s="6" t="s">
-        <v>469</v>
-      </c>
-      <c r="B3" s="5"/>
-      <c r="C3" s="5"/>
-      <c r="D3" s="5"/>
-      <c r="E3" s="5"/>
+      <c r="A3" s="7" t="s">
+        <v>437</v>
+      </c>
+      <c r="B3" s="6"/>
+      <c r="C3" s="6"/>
+      <c r="D3" s="6"/>
+      <c r="E3" s="6"/>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A4" s="1" t="s">
-        <v>410</v>
+        <v>390</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>411</v>
+        <v>391</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>470</v>
+        <v>438</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>471</v>
+        <v>439</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>287</v>
+        <v>277</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="80" x14ac:dyDescent="0.45">
       <c r="A5" s="2" t="s">
-        <v>472</v>
+        <v>440</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>473</v>
+        <v>441</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>474</v>
+        <v>442</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>475</v>
+        <v>443</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>476</v>
+        <v>444</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="80" x14ac:dyDescent="0.45">
       <c r="A6" s="2" t="s">
-        <v>477</v>
+        <v>445</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>478</v>
+        <v>446</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>479</v>
+        <v>447</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>480</v>
+        <v>448</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>481</v>
+        <v>449</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="48" x14ac:dyDescent="0.45">
       <c r="A7" s="2" t="s">
-        <v>482</v>
+        <v>450</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>483</v>
+        <v>451</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>484</v>
+        <v>452</v>
       </c>
       <c r="E7" s="2"/>
     </row>
     <row r="8" spans="1:6" ht="48" x14ac:dyDescent="0.45">
       <c r="A8" s="2" t="s">
-        <v>485</v>
+        <v>453</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>486</v>
+        <v>454</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>487</v>
+        <v>455</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>488</v>
+        <v>456</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>489</v>
+        <v>457</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="48" x14ac:dyDescent="0.45">
       <c r="A9" s="2" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>490</v>
+        <v>458</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>491</v>
+        <v>459</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>492</v>
+        <v>460</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>493</v>
+        <v>461</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A11" s="6" t="s">
-        <v>494</v>
-      </c>
-      <c r="B11" s="5"/>
-      <c r="C11" s="5"/>
-      <c r="D11" s="5"/>
-      <c r="E11" s="5"/>
+      <c r="A11" s="7" t="s">
+        <v>462</v>
+      </c>
+      <c r="B11" s="6"/>
+      <c r="C11" s="6"/>
+      <c r="D11" s="6"/>
+      <c r="E11" s="6"/>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A12" s="1" t="s">
-        <v>495</v>
+        <v>463</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>496</v>
+        <v>464</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>497</v>
+        <v>465</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>498</v>
+        <v>466</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>341</v>
+        <v>326</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A13" s="2" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>499</v>
+        <v>467</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>500</v>
+        <v>468</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>501</v>
+        <v>469</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>502</v>
+        <v>470</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="32" x14ac:dyDescent="0.45">
       <c r="A14" s="2" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>503</v>
+        <v>471</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>504</v>
+        <v>472</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>505</v>
+        <v>473</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>506</v>
+        <v>474</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A15" s="2" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>507</v>
+        <v>475</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>504</v>
+        <v>472</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>508</v>
+        <v>476</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>509</v>
+        <v>477</v>
       </c>
     </row>
     <row r="16" spans="1:6" ht="32" x14ac:dyDescent="0.45">
       <c r="A16" s="2" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>510</v>
+        <v>478</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>504</v>
+        <v>472</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>511</v>
+        <v>479</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>512</v>
+        <v>480</v>
       </c>
     </row>
     <row r="17" spans="1:5" ht="64" x14ac:dyDescent="0.45">
       <c r="A17" s="2" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>513</v>
+        <v>481</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>514</v>
+        <v>482</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>515</v>
+        <v>483</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>516</v>
+        <v>484</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A18" s="8" t="s">
-        <v>517</v>
-      </c>
-      <c r="B18" s="5"/>
-      <c r="C18" s="5"/>
-      <c r="D18" s="5"/>
-      <c r="E18" s="5"/>
+      <c r="A18" s="9" t="s">
+        <v>485</v>
+      </c>
+      <c r="B18" s="6"/>
+      <c r="C18" s="6"/>
+      <c r="D18" s="6"/>
+      <c r="E18" s="6"/>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A20" s="6" t="s">
-        <v>518</v>
-      </c>
-      <c r="B20" s="5"/>
-      <c r="C20" s="5"/>
-      <c r="D20" s="5"/>
-      <c r="E20" s="5"/>
+      <c r="A20" s="7" t="s">
+        <v>486</v>
+      </c>
+      <c r="B20" s="6"/>
+      <c r="C20" s="6"/>
+      <c r="D20" s="6"/>
+      <c r="E20" s="6"/>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A21" s="1" t="s">
-        <v>519</v>
+        <v>487</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>520</v>
+        <v>488</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>521</v>
+        <v>489</v>
       </c>
       <c r="D21" s="1"/>
       <c r="E21" s="1" t="s">
-        <v>341</v>
+        <v>326</v>
       </c>
     </row>
     <row r="22" spans="1:5" ht="32" x14ac:dyDescent="0.45">
       <c r="A22" s="2" t="s">
-        <v>522</v>
+        <v>490</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>523</v>
+        <v>491</v>
       </c>
       <c r="D22" s="2"/>
       <c r="E22" s="2" t="s">
-        <v>524</v>
+        <v>492</v>
       </c>
     </row>
     <row r="23" spans="1:5" ht="80" x14ac:dyDescent="0.45">
       <c r="A23" s="2" t="s">
-        <v>525</v>
+        <v>493</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>526</v>
+        <v>494</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>527</v>
+        <v>495</v>
       </c>
       <c r="D23" s="2"/>
       <c r="E23" s="2" t="s">
-        <v>528</v>
+        <v>496</v>
       </c>
     </row>
     <row r="24" spans="1:5" ht="208" x14ac:dyDescent="0.45">
       <c r="A24" s="2" t="s">
-        <v>529</v>
+        <v>497</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>530</v>
+        <v>498</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>531</v>
+        <v>499</v>
       </c>
       <c r="D24" s="2"/>
       <c r="E24" s="2" t="s">
-        <v>532</v>
+        <v>500</v>
       </c>
     </row>
     <row r="25" spans="1:5" ht="64" x14ac:dyDescent="0.45">
       <c r="A25" s="2" t="s">
-        <v>533</v>
+        <v>501</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>534</v>
+        <v>502</v>
       </c>
       <c r="D25" s="2"/>
       <c r="E25" s="2" t="s">
-        <v>535</v>
+        <v>503</v>
       </c>
     </row>
     <row r="26" spans="1:5" ht="64" x14ac:dyDescent="0.45">
       <c r="A26" s="2" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>536</v>
+        <v>504</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>537</v>
+        <v>505</v>
       </c>
       <c r="D26" s="2"/>
       <c r="E26" s="2" t="s">
-        <v>538</v>
+        <v>506</v>
       </c>
     </row>
     <row r="27" spans="1:5" ht="64" x14ac:dyDescent="0.45">
       <c r="A27" s="2" t="s">
-        <v>539</v>
+        <v>507</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>540</v>
+        <v>508</v>
       </c>
       <c r="D27" s="2"/>
       <c r="E27" s="2" t="s">
-        <v>541</v>
+        <v>509</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A29" s="6" t="s">
-        <v>542</v>
-      </c>
-      <c r="B29" s="5"/>
-      <c r="C29" s="5"/>
-      <c r="D29" s="5"/>
-      <c r="E29" s="5"/>
+      <c r="A29" s="7" t="s">
+        <v>510</v>
+      </c>
+      <c r="B29" s="6"/>
+      <c r="C29" s="6"/>
+      <c r="D29" s="6"/>
+      <c r="E29" s="6"/>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A30" s="1" t="s">
         <v>2</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>543</v>
+        <v>511</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>544</v>
+        <v>512</v>
       </c>
       <c r="D30" s="1"/>
       <c r="E30" s="1"/>
     </row>
     <row r="31" spans="1:5" ht="48" x14ac:dyDescent="0.45">
       <c r="A31" s="2" t="s">
-        <v>545</v>
+        <v>513</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>546</v>
+        <v>514</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>547</v>
+        <v>515</v>
       </c>
       <c r="D31" s="2"/>
       <c r="E31" s="2"/>
     </row>
     <row r="32" spans="1:5" ht="32" x14ac:dyDescent="0.45">
       <c r="A32" s="2" t="s">
-        <v>548</v>
+        <v>516</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>546</v>
+        <v>514</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>549</v>
+        <v>517</v>
       </c>
       <c r="D32" s="2"/>
       <c r="E32" s="2"/>
     </row>
     <row r="33" spans="1:5" ht="64" x14ac:dyDescent="0.45">
       <c r="A33" s="2" t="s">
-        <v>550</v>
+        <v>518</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>551</v>
+        <v>519</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>552</v>
+        <v>520</v>
       </c>
       <c r="D33" s="2"/>
       <c r="E33" s="2"/>
     </row>
     <row r="34" spans="1:5" ht="32" x14ac:dyDescent="0.45">
       <c r="A34" s="2" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>553</v>
+        <v>521</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>554</v>
+        <v>522</v>
       </c>
       <c r="D34" s="2"/>
       <c r="E34" s="2"/>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A35" s="2" t="s">
-        <v>555</v>
+        <v>523</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>556</v>
+        <v>524</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>557</v>
+        <v>525</v>
       </c>
       <c r="D35" s="2"/>
       <c r="E35" s="2"/>
@@ -5342,320 +5173,328 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A1" s="4" t="s">
-        <v>558</v>
-      </c>
-      <c r="B1" s="5"/>
-      <c r="C1" s="5"/>
-      <c r="D1" s="5"/>
-      <c r="E1" s="5"/>
+      <c r="A1" s="5" t="s">
+        <v>526</v>
+      </c>
+      <c r="B1" s="6"/>
+      <c r="C1" s="6"/>
+      <c r="D1" s="6"/>
+      <c r="E1" s="6"/>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A3" s="6" t="s">
-        <v>559</v>
-      </c>
-      <c r="B3" s="5"/>
-      <c r="C3" s="5"/>
-      <c r="D3" s="5"/>
-      <c r="E3" s="5"/>
+      <c r="A3" s="7" t="s">
+        <v>527</v>
+      </c>
+      <c r="B3" s="6"/>
+      <c r="C3" s="6"/>
+      <c r="D3" s="6"/>
+      <c r="E3" s="6"/>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A4" s="1" t="s">
-        <v>560</v>
+        <v>528</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>561</v>
+        <v>529</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>562</v>
+        <v>530</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>563</v>
+        <v>531</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>564</v>
+        <v>532</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="32" x14ac:dyDescent="0.45">
       <c r="A5" s="2" t="s">
-        <v>565</v>
+        <v>533</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>566</v>
+        <v>534</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>567</v>
+        <v>535</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>568</v>
+        <v>536</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>569</v>
+        <v>537</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="32" x14ac:dyDescent="0.45">
       <c r="A6" s="3" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>570</v>
+        <v>538</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>567</v>
+        <v>535</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>571</v>
+        <v>539</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>572</v>
+        <v>540</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="32" x14ac:dyDescent="0.45">
       <c r="A7" s="2" t="s">
-        <v>573</v>
+        <v>541</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>574</v>
+        <v>542</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>567</v>
+        <v>535</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>575</v>
+        <v>543</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>576</v>
+        <v>544</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="32" x14ac:dyDescent="0.45">
       <c r="A8" s="3" t="s">
-        <v>577</v>
+        <v>545</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>578</v>
+        <v>546</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>567</v>
+        <v>535</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>579</v>
+        <v>547</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>580</v>
+        <v>548</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A9" s="2" t="s">
-        <v>581</v>
+        <v>549</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>582</v>
+        <v>550</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>567</v>
+        <v>535</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>583</v>
+        <v>551</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>584</v>
+        <v>552</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A10" s="2" t="s">
-        <v>585</v>
+        <v>553</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>586</v>
+        <v>554</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>567</v>
+        <v>535</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>575</v>
+        <v>543</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>587</v>
+        <v>555</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A11" s="2" t="s">
-        <v>588</v>
+        <v>556</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>589</v>
+        <v>557</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>567</v>
+        <v>535</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>530</v>
+        <v>498</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>587</v>
+        <v>555</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="32" x14ac:dyDescent="0.45">
       <c r="A12" s="2" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>590</v>
+        <v>558</v>
       </c>
       <c r="C12" s="2" t="s">
+        <v>535</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>543</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>559</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A13" s="9" t="s">
+        <v>560</v>
+      </c>
+      <c r="B13" s="6"/>
+      <c r="C13" s="6"/>
+      <c r="D13" s="6"/>
+      <c r="E13" s="6"/>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A15" s="7" t="s">
+        <v>561</v>
+      </c>
+      <c r="B15" s="6"/>
+      <c r="C15" s="6"/>
+      <c r="D15" s="6"/>
+      <c r="E15" s="6"/>
+    </row>
+    <row r="16" spans="1:5" ht="32" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A16" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="C16" s="10" t="s">
+        <v>562</v>
+      </c>
+      <c r="D16" s="11"/>
+      <c r="E16" s="1" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A17" s="2" t="s">
+        <v>563</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>564</v>
+      </c>
+      <c r="C17" s="12" t="s">
+        <v>565</v>
+      </c>
+      <c r="D17" s="13"/>
+      <c r="E17" s="2" t="s">
+        <v>566</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A18" s="2" t="s">
+        <v>545</v>
+      </c>
+      <c r="B18" s="2" t="s">
         <v>567</v>
       </c>
-      <c r="D12" s="2" t="s">
+      <c r="C18" s="12" t="s">
+        <v>568</v>
+      </c>
+      <c r="D18" s="13"/>
+      <c r="E18" s="2" t="s">
+        <v>569</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" ht="32" x14ac:dyDescent="0.45">
+      <c r="A19" s="2" t="s">
+        <v>570</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>571</v>
+      </c>
+      <c r="C19" s="12" t="s">
+        <v>572</v>
+      </c>
+      <c r="D19" s="13"/>
+      <c r="E19" s="2" t="s">
+        <v>573</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" ht="32" x14ac:dyDescent="0.45">
+      <c r="A20" s="2" t="s">
+        <v>574</v>
+      </c>
+      <c r="B20" s="2" t="s">
         <v>575</v>
       </c>
-      <c r="E12" s="2" t="s">
-        <v>591</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A13" s="8" t="s">
-        <v>592</v>
-      </c>
-      <c r="B13" s="5"/>
-      <c r="C13" s="5"/>
-      <c r="D13" s="5"/>
-      <c r="E13" s="5"/>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A15" s="6" t="s">
-        <v>593</v>
-      </c>
-      <c r="B15" s="5"/>
-      <c r="C15" s="5"/>
-      <c r="D15" s="5"/>
-      <c r="E15" s="5"/>
-    </row>
-    <row r="16" spans="1:5" ht="32" x14ac:dyDescent="0.45">
-      <c r="A16" s="1" t="s">
-        <v>160</v>
-      </c>
-      <c r="B16" s="1" t="s">
-        <v>181</v>
-      </c>
-      <c r="C16" s="1" t="s">
-        <v>594</v>
-      </c>
-      <c r="D16" s="1"/>
-      <c r="E16" s="1" t="s">
-        <v>341</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" ht="128" x14ac:dyDescent="0.45">
-      <c r="A17" s="2" t="s">
-        <v>595</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>596</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>597</v>
-      </c>
-      <c r="D17" s="2"/>
-      <c r="E17" s="2" t="s">
-        <v>598</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" ht="96" x14ac:dyDescent="0.45">
-      <c r="A18" s="2" t="s">
+      <c r="C20" s="12" t="s">
+        <v>576</v>
+      </c>
+      <c r="D20" s="13"/>
+      <c r="E20" s="2" t="s">
         <v>577</v>
       </c>
-      <c r="B18" s="2" t="s">
-        <v>599</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>600</v>
-      </c>
-      <c r="D18" s="2"/>
-      <c r="E18" s="2" t="s">
-        <v>601</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" ht="144" x14ac:dyDescent="0.45">
-      <c r="A19" s="2" t="s">
-        <v>602</v>
-      </c>
-      <c r="B19" s="2" t="s">
-        <v>603</v>
-      </c>
-      <c r="C19" s="2" t="s">
-        <v>604</v>
-      </c>
-      <c r="D19" s="2"/>
-      <c r="E19" s="2" t="s">
-        <v>605</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" ht="112" x14ac:dyDescent="0.45">
-      <c r="A20" s="2" t="s">
-        <v>606</v>
-      </c>
-      <c r="B20" s="2" t="s">
-        <v>607</v>
-      </c>
-      <c r="C20" s="2" t="s">
-        <v>608</v>
-      </c>
-      <c r="D20" s="2"/>
-      <c r="E20" s="2" t="s">
-        <v>609</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" ht="80" x14ac:dyDescent="0.45">
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A21" s="2" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>610</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>611</v>
-      </c>
-      <c r="D21" s="2"/>
+        <v>578</v>
+      </c>
+      <c r="C21" s="12" t="s">
+        <v>579</v>
+      </c>
+      <c r="D21" s="13"/>
       <c r="E21" s="2" t="s">
-        <v>612</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" ht="128" x14ac:dyDescent="0.45">
+        <v>580</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A22" s="2" t="s">
-        <v>613</v>
+        <v>581</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>614</v>
-      </c>
-      <c r="C22" s="2" t="s">
-        <v>615</v>
-      </c>
-      <c r="D22" s="2"/>
+        <v>582</v>
+      </c>
+      <c r="C22" s="12" t="s">
+        <v>583</v>
+      </c>
+      <c r="D22" s="13"/>
       <c r="E22" s="2" t="s">
-        <v>616</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" ht="64" x14ac:dyDescent="0.45">
+        <v>584</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A23" s="2" t="s">
-        <v>617</v>
+        <v>585</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>607</v>
-      </c>
-      <c r="C23" s="2" t="s">
-        <v>618</v>
-      </c>
-      <c r="D23" s="2"/>
+        <v>575</v>
+      </c>
+      <c r="C23" s="12" t="s">
+        <v>586</v>
+      </c>
+      <c r="D23" s="13"/>
       <c r="E23" s="2" t="s">
-        <v>619</v>
+        <v>587</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="4">
+  <mergeCells count="12">
+    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="C23:D23"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="C20:D20"/>
+    <mergeCell ref="C21:D21"/>
     <mergeCell ref="A15:E15"/>
     <mergeCell ref="A13:E13"/>
     <mergeCell ref="A1:E1"/>
     <mergeCell ref="A3:E3"/>
+    <mergeCell ref="C16:D16"/>
   </mergeCells>
   <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5674,117 +5513,117 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A1" s="4" t="s">
-        <v>620</v>
-      </c>
-      <c r="B1" s="5"/>
-      <c r="C1" s="5"/>
-      <c r="D1" s="5"/>
+      <c r="A1" s="5" t="s">
+        <v>588</v>
+      </c>
+      <c r="B1" s="6"/>
+      <c r="C1" s="6"/>
+      <c r="D1" s="6"/>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A3" s="6" t="s">
-        <v>621</v>
-      </c>
-      <c r="B3" s="5"/>
-      <c r="C3" s="5"/>
-      <c r="D3" s="5"/>
+      <c r="A3" s="7" t="s">
+        <v>589</v>
+      </c>
+      <c r="B3" s="6"/>
+      <c r="C3" s="6"/>
+      <c r="D3" s="6"/>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A4" s="1" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>3</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>622</v>
+        <v>590</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>287</v>
+        <v>277</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="48" x14ac:dyDescent="0.45">
       <c r="A5" s="2" t="s">
-        <v>623</v>
+        <v>591</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>624</v>
+        <v>592</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>625</v>
+        <v>593</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>626</v>
+        <v>594</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="48" x14ac:dyDescent="0.45">
       <c r="A6" s="2" t="s">
-        <v>627</v>
+        <v>595</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>628</v>
+        <v>596</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>629</v>
+        <v>597</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>630</v>
+        <v>598</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="32" x14ac:dyDescent="0.45">
       <c r="A7" s="2" t="s">
-        <v>631</v>
+        <v>599</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>632</v>
+        <v>600</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>633</v>
+        <v>601</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>634</v>
+        <v>602</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="32" x14ac:dyDescent="0.45">
       <c r="A8" s="2" t="s">
-        <v>635</v>
+        <v>603</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>636</v>
+        <v>604</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>637</v>
+        <v>605</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>638</v>
+        <v>606</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="32" x14ac:dyDescent="0.45">
       <c r="A9" s="2" t="s">
-        <v>639</v>
+        <v>607</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>640</v>
+        <v>608</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>641</v>
+        <v>609</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>642</v>
+        <v>610</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="48" x14ac:dyDescent="0.45">
       <c r="A10" s="2" t="s">
-        <v>643</v>
+        <v>611</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>644</v>
+        <v>612</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>645</v>
+        <v>613</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>646</v>
+        <v>614</v>
       </c>
     </row>
   </sheetData>
@@ -5810,175 +5649,175 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A1" s="4" t="s">
-        <v>647</v>
-      </c>
-      <c r="B1" s="5"/>
-      <c r="C1" s="5"/>
-      <c r="D1" s="5"/>
-      <c r="E1" s="5"/>
-      <c r="F1" s="5"/>
+      <c r="A1" s="5" t="s">
+        <v>615</v>
+      </c>
+      <c r="B1" s="6"/>
+      <c r="C1" s="6"/>
+      <c r="D1" s="6"/>
+      <c r="E1" s="6"/>
+      <c r="F1" s="6"/>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A3" s="6" t="s">
-        <v>648</v>
-      </c>
-      <c r="B3" s="5"/>
-      <c r="C3" s="5"/>
-      <c r="D3" s="5"/>
-      <c r="E3" s="5"/>
+      <c r="A3" s="7" t="s">
+        <v>616</v>
+      </c>
+      <c r="B3" s="6"/>
+      <c r="C3" s="6"/>
+      <c r="D3" s="6"/>
+      <c r="E3" s="6"/>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A4" s="1" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>649</v>
+        <v>617</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>650</v>
+        <v>618</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>521</v>
+        <v>489</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>651</v>
+        <v>619</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="32" x14ac:dyDescent="0.45">
       <c r="A5" s="2" t="s">
-        <v>652</v>
+        <v>620</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>653</v>
+        <v>621</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>654</v>
+        <v>622</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>655</v>
+        <v>623</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>656</v>
+        <v>624</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A6" s="2" t="s">
-        <v>657</v>
+        <v>625</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>658</v>
+        <v>626</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>659</v>
+        <v>627</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>660</v>
+        <v>628</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>661</v>
+        <v>629</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="32" x14ac:dyDescent="0.45">
       <c r="A7" s="2" t="s">
-        <v>662</v>
+        <v>630</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>663</v>
+        <v>631</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>664</v>
+        <v>632</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>665</v>
+        <v>633</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>666</v>
+        <v>634</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="32" x14ac:dyDescent="0.45">
       <c r="A8" s="2" t="s">
-        <v>667</v>
+        <v>635</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>668</v>
+        <v>636</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>669</v>
+        <v>637</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>670</v>
+        <v>638</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>671</v>
+        <v>639</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="48" x14ac:dyDescent="0.45">
       <c r="A9" s="2" t="s">
-        <v>672</v>
+        <v>640</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>673</v>
+        <v>641</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>674</v>
+        <v>642</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>675</v>
+        <v>643</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>676</v>
+        <v>644</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="32" x14ac:dyDescent="0.45">
       <c r="A10" s="2" t="s">
-        <v>677</v>
+        <v>645</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>678</v>
+        <v>646</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>679</v>
+        <v>647</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>680</v>
+        <v>648</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>681</v>
+        <v>649</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="32" x14ac:dyDescent="0.45">
       <c r="A11" s="2" t="s">
-        <v>682</v>
+        <v>650</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>683</v>
+        <v>651</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>684</v>
+        <v>652</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>685</v>
+        <v>653</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>686</v>
+        <v>654</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A12" s="2" t="s">
-        <v>687</v>
+        <v>655</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>688</v>
+        <v>656</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>689</v>
+        <v>657</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>690</v>
+        <v>658</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>691</v>
+        <v>659</v>
       </c>
     </row>
   </sheetData>
@@ -6002,196 +5841,196 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A1" s="4" t="s">
-        <v>692</v>
-      </c>
-      <c r="B1" s="5"/>
-      <c r="C1" s="5"/>
-      <c r="D1" s="5"/>
-      <c r="E1" s="5"/>
-      <c r="F1" s="5"/>
+      <c r="A1" s="5" t="s">
+        <v>660</v>
+      </c>
+      <c r="B1" s="6"/>
+      <c r="C1" s="6"/>
+      <c r="D1" s="6"/>
+      <c r="E1" s="6"/>
+      <c r="F1" s="6"/>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A3" s="6" t="s">
-        <v>693</v>
-      </c>
-      <c r="B3" s="5"/>
-      <c r="C3" s="5"/>
+      <c r="A3" s="7" t="s">
+        <v>661</v>
+      </c>
+      <c r="B3" s="6"/>
+      <c r="C3" s="6"/>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A4" s="1" t="s">
-        <v>694</v>
+        <v>662</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>695</v>
+        <v>663</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>696</v>
+        <v>664</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="48" x14ac:dyDescent="0.45">
       <c r="A5" s="2" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>697</v>
+        <v>665</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="48" x14ac:dyDescent="0.45">
       <c r="A6" s="2" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>698</v>
+        <v>666</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="32" x14ac:dyDescent="0.45">
       <c r="A7" s="2" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>699</v>
+        <v>667</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>700</v>
+        <v>668</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="32" x14ac:dyDescent="0.45">
       <c r="A8" s="2" t="s">
-        <v>701</v>
+        <v>669</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>702</v>
+        <v>670</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="64" x14ac:dyDescent="0.45">
       <c r="A9" s="2" t="s">
-        <v>703</v>
+        <v>671</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>704</v>
+        <v>672</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="64" x14ac:dyDescent="0.45">
       <c r="A10" s="2" t="s">
-        <v>705</v>
+        <v>673</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>706</v>
+        <v>674</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="32" x14ac:dyDescent="0.45">
       <c r="A11" s="2" t="s">
-        <v>707</v>
+        <v>675</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>708</v>
+        <v>676</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>709</v>
+        <v>677</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A13" s="6" t="s">
-        <v>710</v>
-      </c>
-      <c r="B13" s="5"/>
-      <c r="C13" s="5"/>
+      <c r="A13" s="7" t="s">
+        <v>678</v>
+      </c>
+      <c r="B13" s="6"/>
+      <c r="C13" s="6"/>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A14" s="1" t="s">
-        <v>711</v>
+        <v>679</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>712</v>
+        <v>680</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>713</v>
+        <v>681</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A15" s="2" t="s">
-        <v>714</v>
+        <v>682</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>715</v>
+        <v>683</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>716</v>
+        <v>684</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A16" s="2" t="s">
-        <v>717</v>
+        <v>685</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>718</v>
+        <v>686</v>
       </c>
     </row>
     <row r="17" spans="1:3" ht="32" x14ac:dyDescent="0.45">
       <c r="A17" s="2" t="s">
-        <v>719</v>
+        <v>687</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>720</v>
+        <v>688</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>721</v>
+        <v>689</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A18" s="2" t="s">
-        <v>722</v>
+        <v>690</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>723</v>
+        <v>691</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>724</v>
+        <v>692</v>
       </c>
     </row>
     <row r="19" spans="1:3" ht="32" x14ac:dyDescent="0.45">
       <c r="A19" s="2" t="s">
-        <v>725</v>
+        <v>693</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>726</v>
+        <v>694</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A21" s="6" t="s">
-        <v>727</v>
-      </c>
-      <c r="B21" s="5"/>
-      <c r="C21" s="5"/>
+      <c r="A21" s="7" t="s">
+        <v>695</v>
+      </c>
+      <c r="B21" s="6"/>
+      <c r="C21" s="6"/>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A22" s="1" t="s">
-        <v>728</v>
+        <v>696</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>729</v>
+        <v>697</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>3</v>
@@ -6199,46 +6038,46 @@
     </row>
     <row r="23" spans="1:3" ht="48" x14ac:dyDescent="0.45">
       <c r="A23" s="2" t="s">
-        <v>730</v>
+        <v>698</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>567</v>
+        <v>535</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>731</v>
+        <v>699</v>
       </c>
     </row>
     <row r="24" spans="1:3" ht="32" x14ac:dyDescent="0.45">
       <c r="A24" s="2" t="s">
-        <v>732</v>
+        <v>700</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>567</v>
+        <v>535</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>733</v>
+        <v>701</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A25" s="2" t="s">
-        <v>734</v>
+        <v>702</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>735</v>
+        <v>703</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>736</v>
+        <v>704</v>
       </c>
     </row>
     <row r="26" spans="1:3" ht="32" x14ac:dyDescent="0.45">
       <c r="A26" s="2" t="s">
-        <v>737</v>
+        <v>705</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>738</v>
+        <v>706</v>
       </c>
     </row>
   </sheetData>
